--- a/outputs/evaluation/CF_M05_req_eval.xlsx
+++ b/outputs/evaluation/CF_M05_req_eval.xlsx
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9167</v>
+        <v>0.913</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9167</v>
+        <v>0.913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.75</v>
+        <v>0.7188</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9231</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7482</v>
+        <v>0.8046</v>
       </c>
     </row>
     <row r="5">
@@ -635,16 +635,16 @@
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -660,16 +660,16 @@
         <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -685,16 +685,16 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -719,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -744,7 +744,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,126 +987,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R_32</t>
+          <t>R_03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_R25</t>
+          <t>CF_M05_R02</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4553</v>
+        <v>0.5021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No user can access data belonging to other clients.</t>
+          <t>The system shall display a list of applications to which the authenticated user has access.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>R_31</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>No user can access data from other customers.</t>
+          <t>View the portal applications to which the user has access.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>CF_M05_R24</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R_03</t>
+          <t>R_22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M05_R02</t>
+          <t>CF_M05_R15</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4958</v>
+        <v>0.5911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The system shall display a list of applications to which the authenticated user has access.</t>
+          <t>The learning time for new functionalities should not exceed 5 minutes.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>R_21</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>View the portal applications to which the user has access.</t>
+          <t>Learning time for new features should not exceed 5 min.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CF_M01_R14</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R_09</t>
+          <t>R_05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M05_R05</t>
+          <t>CF_M05_R03</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4996</v>
+        <v>0.6103</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The system shall ensure that users cannot access data belonging to other clients.</t>
+          <t>The system shall allow users to access applications from the portal.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Ensure that other customers' data cannot be accessed.</t>
+          <t>Access the applications to which the user has access on the portal.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1148,161 +1148,177 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R_05</t>
+          <t>R_32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M05_R03</t>
+          <t>CF_M05_R25</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5806</v>
+        <v>0.6217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The system shall allow users to access the applications available in the portal.</t>
+          <t>No user can access data from other clients.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>R_31</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Access the applications to which the user has access on the portal.</t>
+          <t>No user can access data from other customers.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CF_M05_R24</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R_22</t>
+          <t>R_07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M05_R15</t>
+          <t>CF_M05_R04</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5976</v>
+        <v>0.6813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The learning time for new functionalities should not exceed 5 minutes.</t>
+          <t>The system shall restrict data visualization and actions (create, modify, delete) based on assigned user roles.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>R_21</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Learning time for new features should not exceed 5 min.</t>
+          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>CF_M01_R14</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>R_19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M05_R04</t>
+          <t>CF_M05_R12</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6766</v>
+        <v>0.6905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>The system shall restrict data visualization and actions (create, modify, delete) based on the user's assigned roles.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+          <t>The application must be available in several languages.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>11b. Personalization and internationalization</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>The application must be available in multiple languages.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>11b. Personalization and internationalization</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
@@ -1318,7 +1334,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6927</v>
+        <v>0.6925</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,202 +1376,210 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R_19</t>
+          <t>R_16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M05_R12</t>
+          <t>CF_M05_R09</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6966</v>
+        <v>0.7353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The application must be available in several languages.</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>11b. Personalization and internationalization</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Design, colors, fonts, and organization must be consistent with the old version.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>R_15</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The application must be available in multiple languages.</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>11b. Personalization and internationalization</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
+          <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CF_M01_R08</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R_16</t>
+          <t>R_31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M05_R09</t>
+          <t>CF_M01_R24</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7376</v>
+        <v>0.7921</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Design, colors, fonts, and organization must be consistent with the old version.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>R_15</t>
-        </is>
-      </c>
+          <t>The application must manage a strict separation of data for each client.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15b. Integrity</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>CF_M01_R08</t>
-        </is>
-      </c>
+          <t>The application must manage a strict separation of data for each customer.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>15b. Integrity</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R_18</t>
+          <t>R_27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M05_R11</t>
+          <t>CF_M05_R20</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7432</v>
+        <v>0.7941</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>80% of users shall not need to ask for third-party help to use the application.</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>R_17</t>
-        </is>
-      </c>
+          <t>The web application must support a large number of concurrent users without degrading its performance.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>12f. Capacity</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>80% of users do not need to ask for help from a third party to do
-use the application.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>CF_M05_R10</t>
-        </is>
-      </c>
+          <t>The web application must support a large number of simultaneous users
+without degrading its performance.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>12f. Capacity</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R_31</t>
+          <t>R_23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M01_R24</t>
+          <t>CF_M05_R16</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.7884</v>
+        <v>0.7951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1564,17 +1588,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The application must manage a strict separation of data for each client.</t>
+          <t>Query operations must have a load time of less than 1 second.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>15b. Integrity</t>
+          <t>12a. Speed and latency</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1590,16 +1614,16 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The application must manage a strict separation of data for each customer.</t>
+          <t>Query operations should have load time lower than 1 second.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>15b. Integrity</t>
+          <t>12a. Speed and latency</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1613,16 +1637,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R_27</t>
+          <t>R_15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M05_R20</t>
+          <t>CF_M05_R08</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7938</v>
+        <v>0.8096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1631,17 +1655,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>The web application must support a large number of concurrent users without degrading its performance.</t>
+          <t>The new content must maintain visual coherence with the design of the old version of the application.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12f. Capacity</t>
+          <t>10a. Appearance</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1657,17 +1681,16 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The web application must support a large number of simultaneous users
-without degrading its performance.</t>
+          <t>The new content must maintain visual consistency with the design of the old version of the application.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>12f. Capacity</t>
+          <t>10a. Appearance</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1681,20 +1704,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R_23</t>
+          <t>R_18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M05_R16</t>
+          <t>CF_M05_R11</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7945</v>
+        <v>0.884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1704,24 +1727,20 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Query operations must have a load time of less than 1 second.</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>12a. Speed and latency</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>80% of users do not need to ask for help from third parties to use the application.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>R_17</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1729,86 +1748,67 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Query operations should have load time lower than 1 second.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>12a. Speed and latency</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
+          <t>80% of users do not need to ask for help from a third party to do
+use the application.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CF_M05_R10</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R_15</t>
+          <t>R_11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M05_R08</t>
+          <t>CF_M05_R06</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.9464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>The new content must maintain visual coherence with the design of the old version of the application.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>10a. Appearance</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>The system shall convert any mention of the old name to the new name.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The new content must maintain visual consistency with the design of the old version of the application.</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>10a. Appearance</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>Convert any mention of the old name to the new name.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8222</v>
+        <v>0.9667</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>The system must have a secure authentication and permission verification mechanism to ensure each user only accesses authorized information and functionalities.</t>
+          <t>The system must have a secure authentication and permission verification mechanism to ensure that each user can only access the information and functionalities that correspond to them.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1874,20 +1874,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R_28</t>
+          <t>R_29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M05_R21</t>
+          <t>CF_M05_R22</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.8794</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1897,20 +1897,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>System availability must be at least 99.9%, even during periods of intensive use.</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>R_27</t>
-        </is>
-      </c>
+          <t>The system must allow the creation, consultation, modification, and deletion of data to authorized users.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1918,214 +1922,226 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>The system must allow the creation, consultation, modification and
+data deletion for authorized users.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R_21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CF_M05_R14</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>The user must be able to perform new operations without special training.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>11c. Learning</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>53</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>The user must be able to perform the new operations without special training.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>11c. Learning</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R_28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CF_M05_R21</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>R_27</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>54</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>System availability must be at least 99.9%, even
 during times of intensive use.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>CF_M05_R20</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>R_26</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CF_M05_R19</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.8794</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>System availability must be at least 99.9%, even during periods of intensive use.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>R_25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>54</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>CF_M05_R18</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R_25</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CF_M05_R18</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.9275</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>The web application must guarantee continuous and stable operation, ensuring its availability at all times.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>12a. Availability</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>54</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>The web application must guarantee continuous and stable operation,
-ensuring its availability at any time.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>12th. Availability</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R_11</t>
+          <t>R_26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M05_R06</t>
+          <t>CF_M05_R19</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9475</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>The system shall convert any mention of the old name to the new name.</t>
+          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>R_25</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Convert any mention of the old name to the new name.</t>
+          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CF_M05_R18</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R_29</t>
+          <t>R_24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M05_R22</t>
+          <t>CF_M05_R17</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.983</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2135,65 +2151,56 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>The system must allow the creation, consultation, modification, and deletion of data for authorized users.</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>15a. Access</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Response time must not exceed 1 second in 95% of queries.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>R_23</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The system must allow the creation, consultation, modification and
-data deletion for authorized users.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>15a. Access</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>Response time should not exceed 1 second in 95% of queries.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CF_M05_R16</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R_20</t>
+          <t>R_17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M05_R13</t>
+          <t>CF_M05_R10</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9849</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2203,20 +2210,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Translations must be complete and correct in both languages.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>R_19</t>
-        </is>
-      </c>
+          <t>The system must be easy to use for any user.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>11a. Ease of use</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -2224,27 +2235,31 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Complete and correct translations in both languages.</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>CF_M05_R12</t>
-        </is>
-      </c>
+          <t>The system must be easy to use for any user.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>11a. Ease of use</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R_24</t>
+          <t>R_20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M05_R17</t>
+          <t>CF_M05_R13</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2257,19 +2272,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Response time must not exceed 1 second in 95% of queries.</t>
+          <t>Complete and correct translations in both languages.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>R_23</t>
+          <t>R_19</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -2283,14 +2298,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Response time should not exceed 1 second in 95% of queries.</t>
+          <t>Complete and correct translations in both languages.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CF_M05_R16</t>
+          <t>CF_M05_R12</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
@@ -2298,12 +2313,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R_21</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M05_R14</t>
+          <t>CF_M05_R18</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2316,17 +2331,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>The user must be able to perform new operations without special training.</t>
+          <t>The web application must guarantee continuous and stable operation, ensuring its availability at any time.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>11c. Learning</t>
+          <t>12a. Availability</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2342,16 +2357,17 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>The user must be able to perform the new operations without special training.</t>
+          <t>The web application must guarantee continuous and stable operation,
+ensuring its availability at any time.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>11c. Learning</t>
+          <t>12th. Availability</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2361,73 +2377,6 @@
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>R_17</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CF_M05_R10</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>The system must be easy to use for any user.</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>11a. Ease of use</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>53</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>The system must be easy to use for any user.</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>11a. Ease of use</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2440,7 +2389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2488,7 +2437,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Upon entering valid credentials, the system shall authenticate the user and grant access to the portal functionalities.</t>
+          <t>The system shall validate user credentials and grant access to the portal upon successful authentication.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2502,7 +2451,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.4626</v>
+        <v>0.4742</v>
       </c>
     </row>
     <row r="3">
@@ -2518,7 +2467,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The system shall only show the applications for which the user has authorized access.</t>
+          <t>The system shall only show applications to which the user has authorized access.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2532,7 +2481,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.5271</v>
+        <v>0.5284</v>
       </c>
     </row>
     <row r="4">
@@ -2548,21 +2497,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>If the user has access to only one application, the system shall redirect them to that application's main page; if multiple, the user shall select the desired application.</t>
+          <t>The system shall redirect the user to the main page of the selected application.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_R03</t>
+          <t>CF_M05_R08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Access the applications to which the user has access on the portal.</t>
+          <t>The new content must maintain visual consistency with the design of the old version of the application.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.3477</v>
+        <v>0.2504</v>
       </c>
     </row>
     <row r="5">
@@ -2578,57 +2527,57 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The system shall verify user roles and permissions upon accessing the Commercial Cloud data management application and permit or deny actions accordingly.</t>
+          <t>The system shall verify user roles and permissions to allow or deny access to specific screens and actions.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_R04</t>
+          <t>CF_M05_R23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
+          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.3048</v>
+        <v>0.2711</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R_10</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The system shall verify the client associated with the user and only display data belonging to that specific client.</t>
+          <t>The system shall prevent access to data belonging to other clients.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_R23</t>
+          <t>CF_M05_R25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
+          <t>No user can access data from other customers.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.1885</v>
+        <v>0.2492</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R_12</t>
+          <t>R_10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2638,81 +2587,111 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The new name shall be displayed in all locations where the old name was previously mentioned.</t>
+          <t>The system shall verify the client associated with the user and only display data belonging to that client.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M05_R06</t>
+          <t>CF_M05_R23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Convert any mention of the old name to the new name.</t>
+          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.4168</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R_13</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The system shall allow administrators to assign or revoke application access for users.</t>
+          <t>The system shall display the new name in all screens and data where the old name was mentioned.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CF_M05_R07</t>
+          <t>CF_M05_R06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Give or remove access to applications from users.</t>
+          <t>Convert any mention of the old name to the new name.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.2541</v>
+        <v>0.4698</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>R_13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The system shall allow administrators to assign or revoke application access for users.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CF_M05_R07</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Give or remove access to applications from users.</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2619</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>R_14</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>criterion</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Upon administrator update, the system shall modify the user's application list, reflecting the changes upon the user's next login.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CF_M05_R04</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1497</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The system shall update the user's application access list upon administrator modification.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CF_M05_R03</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Access the applications to which the user has access on the portal.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2483</v>
       </c>
     </row>
   </sheetData>
@@ -2726,7 +2705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2764,7 +2743,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_R07</t>
+          <t>CF_M05_R05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2774,51 +2753,81 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Give or remove access to applications from users.</t>
+          <t>Ensure that other customers' data cannot be accessed.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R_05</t>
+          <t>R_32</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The system shall allow users to access the applications available in the portal.</t>
+          <t>No user can access data from other clients.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2937</v>
+        <v>0.2694</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>CF_M05_R07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Give or remove access to applications from users.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>R_05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>The system shall allow users to access applications from the portal.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3858</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>CF_M05_R26</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Functionality for generating graphs and interactive panels that represent communication statistics, traffic volume, response times and incidents, facilitating more intuitive and faster analysis.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>R_02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Upon entering valid credentials, the system shall authenticate the user and grant access to the portal functionalities.</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.155</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>R_30</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The system must have a secure authentication and permission verification mechanism to ensure that each user can only access the information and functionalities that correspond to them.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1874</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/CF_M05_req_eval.xlsx
+++ b/outputs/evaluation/CF_M05_req_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.75</v>
+        <v>0.9524</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9231</v>
+        <v>0.8333</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7759</v>
+        <v>0.7806</v>
       </c>
     </row>
     <row r="5">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9583</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="8">
@@ -589,22 +589,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -614,22 +614,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -679,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -704,7 +704,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -854,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4687</v>
+        <v>0.4796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5948</v>
+        <v>0.5647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1057,60 +1057,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R_32</t>
+          <t>R_07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M05_R25</t>
+          <t>CF_M05_R04</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6293</v>
+        <v>0.6939</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No user can access data from other clients.</t>
+          <t>Restrict data visualization and actions (create, modify, delete) based on assigned user roles.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>R_31</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>No user can access data from other customers.</t>
+          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>CF_M05_R24</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1125,7 +1117,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6892</v>
+        <v>0.6965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1184,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6905</v>
+        <v>0.7062</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,244 +1226,261 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>R_23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M05_R04</t>
+          <t>CF_M05_R16</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6923</v>
+        <v>0.7236</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Restrict data visualization and actions (create, modify, delete) based on assigned user roles.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+          <t>Query operations must have a loading time of less than 1 second.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>12a. Speed and latency</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>Query operations should have load time lower than 1 second.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>12a. Speed and latency</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R_23</t>
+          <t>R_03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M05_R16</t>
+          <t>CF_M05_R02</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7197</v>
+        <v>0.7675</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Query operations must have a loading time of less than 1 second.</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>12a. Speed and latency</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>Visualize the applications in the portal to which the user has access.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Query operations should have load time lower than 1 second.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>12a. Speed and latency</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>View the portal applications to which the user has access.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R_16</t>
+          <t>R_31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M05_R09</t>
+          <t>CF_M01_R23</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.7718</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Design, colors, fonts, and organization must be consistent with the old version.</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>R_15</t>
-        </is>
-      </c>
+          <t>The application must manage a strict separation of data for each client.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15b. Integrity</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>CF_M01_R08</t>
-        </is>
-      </c>
+          <t>The application must manage a strict separation of data for each customer.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>15b. Integrity</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R_03</t>
+          <t>R_18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M05_R02</t>
+          <t>CF_M05_R11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7527</v>
+        <v>0.7794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Visualize the applications in the portal to which the user has access.</t>
+          <t>80% of users shall not need to ask for help from third parties to use the application.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>R_17</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>View the portal applications to which the user has access.</t>
+          <t>80% of users do not need to ask for help from a third party to do
+use the application.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CF_M05_R10</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R_31</t>
+          <t>R_27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M01_R24</t>
+          <t>CF_M05_R20</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7915</v>
+        <v>0.7913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1480,17 +1489,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>The application must manage a strict separation of data for each client.</t>
+          <t>The web application must support a large number of concurrent users without degrading its performance.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15b. Integrity</t>
+          <t>12f. Capacity</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1506,16 +1515,17 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>The application must manage a strict separation of data for each customer.</t>
+          <t>The web application must support a large number of simultaneous users
+without degrading its performance.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15b. Integrity</t>
+          <t>12f. Capacity</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1529,16 +1539,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R_27</t>
+          <t>R_15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M05_R20</t>
+          <t>CF_M05_R08</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.7919</v>
+        <v>0.8127</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1547,17 +1557,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The web application must support a large number of concurrent users without degrading its performance.</t>
+          <t>The new content must maintain visual coherence with the design of the old version of the application.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12f. Capacity</t>
+          <t>10a. Appearance</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1573,17 +1583,16 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The web application must support a large number of simultaneous users
-without degrading its performance.</t>
+          <t>The new content must maintain visual consistency with the design of the old version of the application.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>12f. Capacity</t>
+          <t>10a. Appearance</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1597,143 +1606,143 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R_18</t>
+          <t>R_29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M05_R11</t>
+          <t>CF_M05_R22</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7993</v>
+        <v>0.8671</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>80% of users shall not need to ask for help from third parties to use the application.</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>R_17</t>
-        </is>
-      </c>
+          <t>The system must allow the creation, query, modification, and deletion of data for authorized users.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>80% of users do not need to ask for help from a third party to do
-use the application.</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>CF_M05_R10</t>
-        </is>
-      </c>
+          <t>The system must allow the creation, consultation, modification and
+data deletion for authorized users.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R_15</t>
+          <t>R_24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M05_R08</t>
+          <t>CF_M05_R17</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8098</v>
+        <v>0.8754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>The new content must maintain visual coherence with the design of the old version of the application.</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>10a. Appearance</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Response time shall not exceed 1 second in 95% of queries.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>R_23</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The new content must maintain visual consistency with the design of the old version of the application.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>10a. Appearance</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
+          <t>Response time should not exceed 1 second in 95% of queries.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CF_M05_R16</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R_30</t>
+          <t>R_28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M05_R23</t>
+          <t>CF_M05_R21</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8217</v>
+        <v>0.8827</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1747,14 +1756,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>The system must have a secure authentication and permission verification mechanism to ensure each user only accesses authorized information and functionalities.</t>
+          <t>System availability must be at least 99.9%, even during periods of intensive use.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>R_29</t>
+          <t>R_27</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1768,14 +1777,15 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
+          <t>System availability must be at least 99.9%, even
+during times of intensive use.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CF_M05_R22</t>
+          <t>CF_M05_R20</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
@@ -1783,20 +1793,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R_29</t>
+          <t>R_26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M05_R22</t>
+          <t>CF_M05_R19</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8539</v>
+        <v>0.8827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1806,24 +1816,20 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>The system must allow the creation, query, modification, and deletion of data for authorized users.</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>15a. Access</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>System availability must be at least 99.9%, even during periods of intensive use.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>R_25</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1831,100 +1837,86 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The system must allow the creation, consultation, modification and
-data deletion for authorized users.</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>15a. Access</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CF_M05_R18</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R_28</t>
+          <t>R_01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M05_R21</t>
+          <t>CF_M05_R01</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.8821</v>
+        <v>0.8883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>System availability must be at least 99.9%, even during periods of intensive use.</t>
+          <t>Access the portal using personal credentials authentication.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>R_27</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>System availability must be at least 99.9%, even
-during times of intensive use.</t>
+          <t>Access the portal using credential authentication personal.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>CF_M05_R20</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R_26</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M05_R19</t>
+          <t>CF_M05_R18</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8821</v>
+        <v>0.922</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1934,20 +1926,28 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>System availability must be at least 99.9%, even during periods of intensive use.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>R_25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>The web application must guarantee continuous and stable operation, ensuring its availability at all times.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>12a. Availability</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Requirement was labeled as 12a. Availability, which is a sub-characteristic of Reliability in ISO/IEC 25010, but categorized as Volere in the document.</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1955,86 +1955,107 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>CF_M05_R18</t>
-        </is>
-      </c>
+          <t>The web application must guarantee continuous and stable operation,
+ensuring its availability at any time.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>12th. Availability</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R_01</t>
+          <t>R_21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M05_R01</t>
+          <t>CF_M05_R14</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.8824</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Access the portal using personal credentials authentication.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+          <t>The user must be able to perform new operations without special training.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>11c. Learning</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Access the portal using credential authentication personal.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+          <t>The user must be able to perform the new operations without special training.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>11c. Learning</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R_24</t>
+          <t>R_17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M05_R17</t>
+          <t>CF_M05_R10</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9002</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2044,20 +2065,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Response time shall not exceed 1 second in 95% of queries.</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>R_23</t>
-        </is>
-      </c>
+          <t>The system must be easy to use for any user.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>11a. Ease of use</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -2065,333 +2090,72 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Response time should not exceed 1 second in 95% of queries.</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>CF_M05_R16</t>
-        </is>
-      </c>
+          <t>The system must be easy to use for any user.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>11a. Ease of use</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R_25</t>
+          <t>R_11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M05_R18</t>
+          <t>CF_M05_R06</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9264</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>The web application must guarantee continuous and stable operation, ensuring its availability at all times.</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>12a. Availability</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>Convert any mention of the old name to the new name.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Requirement was labeled as 12a. Availability, which is a sub-characteristic of Reliability in ISO/IEC 25010, but categorized as Volere in the document.</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The web application must guarantee continuous and stable operation,
-ensuring its availability at any time.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>12th. Availability</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>Convert any mention of the old name to the new name.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>R_20</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CF_M05_R13</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.9839</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Translations must be complete and correct in both languages.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>R_19</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>53</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Complete and correct translations in both languages.</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>CF_M05_R12</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>R_21</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CF_M05_R14</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>The user must be able to perform new operations without special training.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>11c. Learning</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>53</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>The user must be able to perform the new operations without special training.</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>11c. Learning</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>R_17</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CF_M05_R10</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>The system must be easy to use for any user.</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>11a. Ease of use</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>53</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>The system must be easy to use for any user.</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>11a. Ease of use</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>R_11</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CF_M05_R06</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Convert any mention of the old name to the new name.</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>50</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Convert any mention of the old name to the new name.</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2404,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2442,241 +2206,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R_02</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The system shall validate user credentials and grant access to the portal if they are valid.</t>
+          <t>Restrict access between clients.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M05_R01</t>
+          <t>CF_M05_R03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Access the portal using credential authentication personal.</t>
+          <t>Access the applications to which the user has access on the portal.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.3083</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>R_04</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>The system shall display a list of applications corresponding to the user's access permissions upon login.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CF_M05_R23</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.2906</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>R_06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>The system shall redirect the user to the main page of the selected application.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CF_M05_R08</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>The new content must maintain visual consistency with the design of the old version of the application.</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.2606</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>R_08</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>The system shall verify user roles and permissions to allow or deny access to specific screens and data actions.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CF_M05_R04</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.2685</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>R_09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Restrict access between clients.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CF_M05_R04</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1801</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>R_10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>The system shall ensure that users can only access data associated with their specific client.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CF_M05_R23</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.2713</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>R_12</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>The system shall display the new name in all screens and data where the old name was mentioned.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CF_M05_R06</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Convert any mention of the old name to the new name.</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0.4602</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>R_14</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>The system shall update the user's access list upon administrator confirmation, reflecting changes in the portal.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CF_M05_R03</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Access the applications to which the user has access on the portal.</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.2565</v>
+        <v>0.1895</v>
       </c>
     </row>
   </sheetData>
@@ -2690,7 +2244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2728,7 +2282,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_R05</t>
+          <t>CF_M05_R04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2743,46 +2297,106 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R_32</t>
+          <t>R_05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>No user can access data from other clients.</t>
+          <t>Access applications from the portal.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2808</v>
+        <v>0.0881</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_R26</t>
+          <t>CF_M05_R09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>R_15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>The new content must maintain visual coherence with the design of the old version of the application.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3294</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CF_M05_R13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Complete and correct translations in both languages.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>R_19</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The application must be available in several languages.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2801</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M05_R24</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Functionality for generating graphs and interactive panels that represent communication statistics, traffic volume, response times and incidents, facilitating more intuitive and faster analysis.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>R_30</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>The system must have a secure authentication and permission verification mechanism to ensure each user only accesses authorized information and functionalities.</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.146</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>R_22</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The learning time for new functionalities should not exceed 5 minutes.</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1506</v>
       </c>
     </row>
   </sheetData>
